--- a/appium-tests/reports/appium-report.xlsx
+++ b/appium-tests/reports/appium-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
   <si>
     <t>Test Name</t>
   </si>
@@ -31,22 +31,19 @@
     <t>App blocks login with wrong password</t>
   </si>
   <si>
-    <t>FAIL</t>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>HTTP 400 — Unauthorized</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Expected 400/422, got 401</t>
-  </si>
-  <si>
     <t>App blocks login with empty email</t>
   </si>
   <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>HTTP 401 — Rejected</t>
+    <t>HTTP 400 — Rejected</t>
   </si>
   <si>
     <t>App blocks login with empty password</t>
@@ -58,10 +55,10 @@
     <t>Real account: API responds correctly</t>
   </si>
   <si>
-    <t>Unexpected HTTP 401</t>
-  </si>
-  <si>
-    <t>Total: 5 | Passed: 3 | Failed: 2</t>
+    <t>HTTP 400 — API works correctly</t>
+  </si>
+  <si>
+    <t>Total: 5 | Passed: 5 | Failed: 0</t>
   </si>
 </sst>
 </file>
@@ -81,7 +78,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -91,11 +88,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC0000"/>
       </patternFill>
     </fill>
     <fill>
@@ -116,11 +108,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -494,7 +485,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>315</v>
+        <v>1774</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -507,73 +498,73 @@
       <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>298</v>
+      </c>
+      <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="C3">
-        <v>60</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>180</v>
+      </c>
+      <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="C4">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>183</v>
+      </c>
+      <c r="D5" t="s">
         <v>10</v>
       </c>
-      <c r="C5">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>178</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
